--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260609.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260609.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.95%</t>
+          <t>10.51%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.98%</t>
+          <t>10.17%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>378,356,486</t>
+          <t>377,008,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>6.51%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.23%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.17%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>186,185,000</t>
+          <t>185,521,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.76%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -765,56 +765,56 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,028,000</t>
+          <t>5,010,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.72%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>134,749,945</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>135,231,945</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -853,100 +853,100 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>29,676,000</t>
+          <t>29,270,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -963,56 +963,56 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>228,380,516</t>
+          <t>227,566,516</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>25,984,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>26,076,000</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>62,856,000</t>
+          <t>62,675,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1166,90 +1166,90 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>48,547,000</t>
+          <t>319,175,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>314,175,000</t>
+          <t>48,547,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>85,399,080</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>85,399,080</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,22 +1261,22 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>28,577,829,774</t>
+          <t>28,892,324,223</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,481,619,327</t>
+          <t>10,288,502,127</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-3,836,776,154</t>
+          <t>-4,401,820,861</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
